--- a/runs/ceattle/GOA_24_pollock_single_species_1970-2024.xlsx
+++ b/runs/ceattle/GOA_24_pollock_single_species_1970-2024.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11207"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10413"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/grantadams/Documents/GitHub/Rceattle-models/EBS pk/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jim/_mymods/noaa-afsc/EBS_pollock/runs/ceattle/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B036B571-D942-084E-95B8-386BB9FC848D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C720796-18B3-4C4C-902A-6E8CBED70D2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="760" windowWidth="27520" windowHeight="13120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="760" windowWidth="27520" windowHeight="13120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="meta_data" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
     <sheet name="Pyrs" sheetId="18" r:id="rId18"/>
     <sheet name="UobsWtAge" sheetId="19" r:id="rId19"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
 </workbook>
 </file>
 
